--- a/MR_UKBiobank/BinaryData/Logistic/MR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/Logistic/MR_dat.xlsx
@@ -6,18 +6,18 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hypertension" r:id="rId3" sheetId="1"/>
-    <sheet name="Fracture" r:id="rId4" sheetId="2"/>
-    <sheet name="CAD" r:id="rId5" sheetId="3"/>
-    <sheet name="MI" r:id="rId6" sheetId="4"/>
-    <sheet name="IS" r:id="rId7" sheetId="5"/>
+    <sheet name="Fracture" r:id="rId3" sheetId="1"/>
+    <sheet name="CAD" r:id="rId4" sheetId="2"/>
+    <sheet name="MI" r:id="rId5" sheetId="3"/>
+    <sheet name="IS" r:id="rId6" sheetId="4"/>
+    <sheet name="Hypertension" r:id="rId7" sheetId="5"/>
     <sheet name="T2DM" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="50">
   <si>
     <t>SNP</t>
   </si>
@@ -85,9 +85,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -148,25 +145,25 @@
     <t>FALSE</t>
   </si>
   <si>
+    <t>Fracture</t>
+  </si>
+  <si>
+    <t>Sclerostin</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>Hypertension</t>
-  </si>
-  <si>
-    <t>Sclerostin</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>Fracture</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>IS</t>
   </si>
   <si>
     <t>T2DM</t>
@@ -294,34 +291,31 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0075423328999804536</v>
+        <v>0.05852301000398645</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
@@ -330,28 +324,28 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
         <v>42</v>
       </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
-      </c>
       <c r="O2" t="n">
-        <v>0.008572143944722537</v>
+        <v>0.014706108026039059</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3789322279754317</v>
+        <v>6.90593110046539E-5</v>
       </c>
       <c r="Q2" t="n">
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -363,48 +357,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.641269727342004E-4</v>
+        <v>-0.06057742191195994</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
@@ -413,28 +404,28 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.007259920288599034</v>
+        <v>0.012263825341104383</v>
       </c>
       <c r="P3" t="n">
-        <v>0.927112350301289</v>
+        <v>7.831473916187852E-7</v>
       </c>
       <c r="Q3" t="n">
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -446,48 +437,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0026409784804478855</v>
+        <v>0.08657116914557775</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
@@ -496,28 +484,28 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.009614765491649134</v>
+        <v>0.016678973778723176</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7835625219492152</v>
+        <v>2.098006599721131E-7</v>
       </c>
       <c r="Q4" t="n">
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -529,48 +517,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.017835853848220305</v>
+        <v>-0.09435562977425106</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
@@ -579,28 +564,28 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s">
         <v>42</v>
       </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s">
-        <v>43</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.010249286011494803</v>
+        <v>0.017888019338047623</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08182311216962376</v>
+        <v>1.3290477895093088E-7</v>
       </c>
       <c r="Q5" t="n">
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -612,48 +597,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.005059415101179245</v>
+        <v>-0.055310828736900575</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
@@ -662,28 +644,28 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" t="s">
         <v>42</v>
       </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
-      </c>
       <c r="O6" t="n">
-        <v>0.007187042130393239</v>
+        <v>0.012175680748497439</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4814555245876734</v>
+        <v>5.5530388485653914E-6</v>
       </c>
       <c r="Q6" t="n">
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -695,48 +677,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.015763325962053525</v>
+        <v>-0.09961683158859869</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
@@ -745,28 +724,28 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" t="s">
         <v>42</v>
       </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" t="s">
-        <v>43</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.009870504839532435</v>
+        <v>0.017231222866866014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1102627774549187</v>
+        <v>7.417768735741478E-9</v>
       </c>
       <c r="Q7" t="n">
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -778,21 +757,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -883,34 +859,31 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05852301000398645</v>
+        <v>-0.022876151624338956</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
@@ -919,28 +892,28 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>0.014706108026039059</v>
+        <v>0.015523722780576893</v>
       </c>
       <c r="P2" t="n">
-        <v>6.90593110046539E-5</v>
+        <v>0.14058248846438318</v>
       </c>
       <c r="Q2" t="n">
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -952,48 +925,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06057742191195994</v>
+        <v>0.024538082625255815</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
@@ -1002,28 +972,28 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>0.012263825341104383</v>
+        <v>0.013236359345181076</v>
       </c>
       <c r="P3" t="n">
-        <v>7.831473916187852E-7</v>
+        <v>0.06376215971987187</v>
       </c>
       <c r="Q3" t="n">
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1035,48 +1005,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08657116914557775</v>
+        <v>-0.018248869437388706</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
@@ -1085,28 +1052,28 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
-        <v>0.016678973778723176</v>
+        <v>0.017419398346154382</v>
       </c>
       <c r="P4" t="n">
-        <v>2.098006599721131E-7</v>
+        <v>0.29481479490083357</v>
       </c>
       <c r="Q4" t="n">
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1118,48 +1085,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09435562977425106</v>
+        <v>0.03355083544427332</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
@@ -1168,28 +1132,28 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O5" t="n">
-        <v>0.017888019338047623</v>
+        <v>0.018499962349236128</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3290477895093088E-7</v>
+        <v>0.06974512920472323</v>
       </c>
       <c r="Q5" t="n">
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1201,48 +1165,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.055310828736900575</v>
+        <v>0.031249891139248732</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
@@ -1251,28 +1212,28 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
-        <v>0.012175680748497439</v>
+        <v>0.013088108419160105</v>
       </c>
       <c r="P6" t="n">
-        <v>5.5530388485653914E-6</v>
+        <v>0.016956238109518375</v>
       </c>
       <c r="Q6" t="n">
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1284,48 +1245,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09961683158859869</v>
+        <v>0.028143938473642677</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
@@ -1334,28 +1292,28 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>0.017231222866866014</v>
+        <v>0.017841604329860948</v>
       </c>
       <c r="P7" t="n">
-        <v>7.417768735741478E-9</v>
+        <v>0.11469588818011912</v>
       </c>
       <c r="Q7" t="n">
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1367,21 +1325,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1472,34 +1427,31 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.022876151624338956</v>
+        <v>-0.018461384409979027</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
@@ -1508,28 +1460,28 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>0.015523722780576893</v>
+        <v>0.019048266001714085</v>
       </c>
       <c r="P2" t="n">
-        <v>0.14058248846438318</v>
+        <v>0.3324505178076055</v>
       </c>
       <c r="Q2" t="n">
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1541,48 +1493,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.024538082625255815</v>
+        <v>0.03261748736920863</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
@@ -1591,28 +1540,28 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>0.013236359345181076</v>
+        <v>0.01624168933907146</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06376215971987187</v>
+        <v>0.044615981774844375</v>
       </c>
       <c r="Q3" t="n">
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1624,48 +1573,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.018248869437388706</v>
+        <v>-0.027049316458251003</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
@@ -1674,28 +1620,28 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O4" t="n">
-        <v>0.017419398346154382</v>
+        <v>0.02129732964239767</v>
       </c>
       <c r="P4" t="n">
-        <v>0.29481479490083357</v>
+        <v>0.20405606765255724</v>
       </c>
       <c r="Q4" t="n">
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1707,48 +1653,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03355083544427332</v>
+        <v>-0.0019502379566337326</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
@@ -1757,28 +1700,28 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>0.018499962349236128</v>
+        <v>0.022910329051921627</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06974512920472323</v>
+        <v>0.9321621473110449</v>
       </c>
       <c r="Q5" t="n">
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1790,48 +1733,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.031249891139248732</v>
+        <v>0.02159258312629346</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
@@ -1840,28 +1780,28 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>0.013088108419160105</v>
+        <v>0.01604694773513733</v>
       </c>
       <c r="P6" t="n">
-        <v>0.016956238109518375</v>
+        <v>0.17843536714676128</v>
       </c>
       <c r="Q6" t="n">
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1873,48 +1813,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.028143938473642677</v>
+        <v>0.00876437411683533</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
@@ -1923,28 +1860,28 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>0.017841604329860948</v>
+        <v>0.021987228070259737</v>
       </c>
       <c r="P7" t="n">
-        <v>0.11469588818011912</v>
+        <v>0.6901790792852229</v>
       </c>
       <c r="Q7" t="n">
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1956,21 +1893,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2061,34 +1995,31 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.018461384409979027</v>
+        <v>0.007015026789195248</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
@@ -2097,28 +2028,28 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.019048266001714085</v>
+        <v>0.029314722086765454</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3324505178076055</v>
+        <v>0.810872600565911</v>
       </c>
       <c r="Q2" t="n">
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2130,48 +2061,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03261748736920863</v>
+        <v>-0.012385428496962397</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
@@ -2180,28 +2108,28 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01624168933907146</v>
+        <v>0.024770176724765183</v>
       </c>
       <c r="P3" t="n">
-        <v>0.044615981774844375</v>
+        <v>0.6170654086327142</v>
       </c>
       <c r="Q3" t="n">
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2213,48 +2141,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.027049316458251003</v>
+        <v>0.0030275900167045025</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
@@ -2263,28 +2188,28 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02129732964239767</v>
+        <v>0.032857782726198936</v>
       </c>
       <c r="P4" t="n">
-        <v>0.20405606765255724</v>
+        <v>0.9265850208984425</v>
       </c>
       <c r="Q4" t="n">
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2296,48 +2221,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0019502379566337326</v>
+        <v>0.007581424790600065</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
@@ -2346,28 +2268,28 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.022910329051921627</v>
+        <v>0.034939301597954366</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9321621473110449</v>
+        <v>0.8282173484673135</v>
       </c>
       <c r="Q5" t="n">
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2379,48 +2301,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02159258312629346</v>
+        <v>-0.016101449522963038</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
@@ -2429,28 +2348,28 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01604694773513733</v>
+        <v>0.024536669273799668</v>
       </c>
       <c r="P6" t="n">
-        <v>0.17843536714676128</v>
+        <v>0.5116826763564092</v>
       </c>
       <c r="Q6" t="n">
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2462,48 +2381,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00876437411683533</v>
+        <v>-0.012755970865085</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
@@ -2512,28 +2428,28 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.021987228070259737</v>
+        <v>0.03387531050553985</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6901790792852229</v>
+        <v>0.7065031650257299</v>
       </c>
       <c r="Q7" t="n">
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2545,21 +2461,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2650,34 +2563,31 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007015026789195248</v>
+        <v>0.0075423328999804536</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
@@ -2686,28 +2596,28 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.029314722086765454</v>
+        <v>0.008572143944722537</v>
       </c>
       <c r="P2" t="n">
-        <v>0.810872600565911</v>
+        <v>0.3789322279754317</v>
       </c>
       <c r="Q2" t="n">
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2719,48 +2629,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.012385428496962397</v>
+        <v>-6.641269727342004E-4</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
@@ -2769,28 +2676,28 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.024770176724765183</v>
+        <v>0.007259920288599034</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6170654086327142</v>
+        <v>0.927112350301289</v>
       </c>
       <c r="Q3" t="n">
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2802,48 +2709,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0030275900167045025</v>
+        <v>-0.0026409784804478855</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
@@ -2852,28 +2756,28 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.032857782726198936</v>
+        <v>0.009614765491649134</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9265850208984425</v>
+        <v>0.7835625219492152</v>
       </c>
       <c r="Q4" t="n">
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2885,48 +2789,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007581424790600065</v>
+        <v>0.017835853848220305</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
@@ -2935,28 +2836,28 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.034939301597954366</v>
+        <v>0.010249286011494803</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8282173484673135</v>
+        <v>0.08182311216962376</v>
       </c>
       <c r="Q5" t="n">
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2968,48 +2869,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.016101449522963038</v>
+        <v>-0.005059415101179245</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
@@ -3018,28 +2916,28 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.024536669273799668</v>
+        <v>0.007187042130393239</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5116826763564092</v>
+        <v>0.4814555245876734</v>
       </c>
       <c r="Q6" t="n">
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3051,48 +2949,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.012755970865085</v>
+        <v>0.015763325962053525</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
@@ -3101,28 +2996,28 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03387531050553985</v>
+        <v>0.009870504839532435</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7065031650257299</v>
+        <v>0.1102627774549187</v>
       </c>
       <c r="Q7" t="n">
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3134,21 +3029,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3239,28 +3131,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -3275,16 +3164,16 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.014156466496240019</v>
@@ -3296,7 +3185,7 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3308,42 +3197,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -3358,16 +3244,16 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>0.012085688651311455</v>
@@ -3379,7 +3265,7 @@
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3391,42 +3277,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -3441,16 +3324,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0.015820910871693763</v>
@@ -3462,7 +3345,7 @@
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3474,42 +3357,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -3524,16 +3404,16 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
         <v>0.0169437037706899</v>
@@ -3545,7 +3425,7 @@
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3557,42 +3437,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -3607,16 +3484,16 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0.011956358439186417</v>
@@ -3628,7 +3505,7 @@
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3640,42 +3517,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -3690,16 +3564,16 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
         <v>0.016358578357047373</v>
@@ -3711,7 +3585,7 @@
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3723,21 +3597,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/MR_UKBiobank/BinaryData/Logistic/MR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/Logistic/MR_dat.xlsx
@@ -392,7 +392,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.06057742191195994</v>
@@ -434,7 +434,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -552,7 +552,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.09435562977425106</v>
@@ -594,7 +594,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -712,7 +712,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.09961683158859869</v>
@@ -754,7 +754,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -960,7 +960,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.024538082625255815</v>
@@ -1002,7 +1002,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1120,7 +1120,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.03355083544427332</v>
@@ -1162,7 +1162,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1280,7 +1280,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.028143938473642677</v>
@@ -1322,7 +1322,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -1528,7 +1528,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.03261748736920863</v>
@@ -1570,7 +1570,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1688,7 +1688,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0019502379566337326</v>
@@ -1730,7 +1730,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1848,7 +1848,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.00876437411683533</v>
@@ -1890,7 +1890,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2096,7 +2096,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.012385428496962397</v>
@@ -2138,7 +2138,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2256,7 +2256,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.007581424790600065</v>
@@ -2298,7 +2298,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -2416,7 +2416,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.012755970865085</v>
@@ -2458,7 +2458,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2664,7 +2664,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-6.641269727342004E-4</v>
@@ -2706,7 +2706,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2824,7 +2824,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.017835853848220305</v>
@@ -2866,7 +2866,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -2984,7 +2984,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.015763325962053525</v>
@@ -3026,7 +3026,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -3232,7 +3232,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.013143179423704222</v>
@@ -3274,7 +3274,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -3392,7 +3392,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.02506469891272249</v>
@@ -3434,7 +3434,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -3552,7 +3552,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.0161210675852458</v>
@@ -3594,7 +3594,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
